--- a/signup_forms/044_religious_study_group_application_form--signup_forms.xlsx
+++ b/signup_forms/044_religious_study_group_application_form--signup_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1171,8 +1171,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1217,12 +1217,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1251,12 +1251,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1268,12 +1268,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'small'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Small'}</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'large'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Large'}</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
@@ -1336,12 +1336,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'bible_study'}</t>
+          <t>bible_study</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Bible Study'}</t>
+          <t>Bible Study</t>
         </is>
       </c>
     </row>
@@ -1404,12 +1404,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'prayer_group'}</t>
+          <t>prayer_group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Prayer Group'}</t>
+          <t>Prayer Group</t>
         </is>
       </c>
     </row>
@@ -1421,12 +1421,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'book_club'}</t>
+          <t>book_club</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Book Club'}</t>
+          <t>Book Club</t>
         </is>
       </c>
     </row>
@@ -1438,12 +1438,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1455,12 +1455,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1472,12 +1472,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1506,12 +1506,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1523,12 +1523,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1540,12 +1540,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1591,12 +1591,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1608,12 +1608,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1659,12 +1659,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1676,12 +1676,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1693,12 +1693,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1710,12 +1710,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1727,12 +1727,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
